--- a/InputData/indst/BSoAIGtAP/BAU Shr of Ag Indst Going to Anml Prdcts.xlsx
+++ b/InputData/indst/BSoAIGtAP/BAU Shr of Ag Indst Going to Anml Prdcts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\next\Dropbox\NEXT Group\20. 프로젝트 관리\2025 에너지 수요전망 모형 구축\EPS 모형\eps-southkorea-3.3.1\InputData\indst\BSoAIGtAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\administer\Dropbox\kjh\2025\02. EPS\EI\251020_메일회신\회신용 파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C104260-96EC-4FE8-9C39-B9EBF534C3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB51909-ED00-4695-9530-7F0824A290FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
   <si>
     <t>Source:</t>
   </si>
@@ -70,18 +70,6 @@
     <t>U.S. Department of Agriculture</t>
   </si>
   <si>
-    <t>2017 Census of Agriculture</t>
-  </si>
-  <si>
-    <t>https://www.nass.usda.gov/Quick_Stats/CDQT/chapter/1/table/2/state/US</t>
-  </si>
-  <si>
-    <t>Chapter 1, Table 2</t>
-  </si>
-  <si>
-    <t>2017 Census of Agriculture data:</t>
-  </si>
-  <si>
     <t>Some of the crop sales are for animals (primarily animal feed).</t>
   </si>
   <si>
@@ -137,9 +125,6 @@
   </si>
   <si>
     <t>n/a</t>
-  </si>
-  <si>
-    <t>M$</t>
   </si>
   <si>
     <t>Excludes exports</t>
@@ -210,13 +195,60 @@
   <si>
     <t>USDA Agricultural Projections to 2028</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korea Rural Economic Institute (KREI)</t>
+  </si>
+  <si>
+    <t>https://www.krei.re.kr/krei/page/24?cmd=view&amp;pst=165349&amp;pageIndex=1</t>
+  </si>
+  <si>
+    <t>Attachment 2. Projected Values of Major Aggregate Indicators (Page 12)</t>
+  </si>
+  <si>
+    <t>Feed shares and market sizes of main crops</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">— This analysis is based on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>U.S. data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Normal year (average of 2019–2023 actual results) Census of Agriculture data:</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trillion KRW (Korean won)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,6 +281,30 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -295,7 +351,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -314,6 +370,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="1" builtinId="5"/>
@@ -331,6 +391,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>629627</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>29193</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE1DF5AA-F13E-51D9-0D76-D24962F734BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7543800"/>
+          <a:ext cx="7001852" cy="4429743"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -596,18 +705,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="68.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,111 +724,115 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>53</v>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -728,115 +841,112 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.4140625" customWidth="1"/>
-    <col min="3" max="3" width="26.4140625" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="25.375" customWidth="1"/>
+    <col min="3" max="3" width="26.375" customWidth="1"/>
     <col min="4" max="4" width="25.25" customWidth="1"/>
-    <col min="5" max="5" width="21.1640625" customWidth="1"/>
-    <col min="6" max="6" width="23.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.125" customWidth="1"/>
+    <col min="6" max="6" width="23.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9">
-        <f>388522695000/10^6</f>
-        <v>388522.69500000001</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B3" s="12">
+        <v>558</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9">
-        <f>193546699000/10^6</f>
-        <v>193546.69899999999</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B4" s="14">
+        <v>324</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="9">
-        <f>194975996000/10^6</f>
-        <v>194975.99600000001</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B5" s="14">
+        <v>231</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F13" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>5302</v>
@@ -856,9 +966,9 @@
         <v>41512.799999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -878,9 +988,9 @@
         <v>527.88</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -900,9 +1010,9 @@
         <v>706.26</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>68</v>
@@ -919,9 +1029,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>50</v>
@@ -941,12 +1051,12 @@
         <v>5088.16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C20">
         <v>21200</v>
@@ -962,15 +1072,15 @@
         <v>6360</v>
       </c>
       <c r="G20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <f>34800/10^3</f>
@@ -987,12 +1097,12 @@
         <v>12005.999999999998</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1012,9 +1122,9 @@
         <v>1698.48</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1034,9 +1144,9 @@
         <v>2768.6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1056,9 +1166,9 @@
         <v>1454.36</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1078,9 +1188,9 @@
         <v>967.19999999999993</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1093,46 +1203,47 @@
         <v>0</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F26">
         <v>51587</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <f>SUMPRODUCT(D15:D26,F15:F26)/SUM(F15:F26)</f>
         <v>0.24377594409350131</v>
       </c>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D30" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B32" s="3"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <f>(B5/B3)+A29*(B4/B3)</f>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1142,15 +1253,15 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AH2"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B1" s="7">
         <v>2018</v>
@@ -1252,141 +1363,141 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <f>Data!A33</f>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="C2">
         <f>$B2</f>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="D2">
         <f t="shared" ref="D2:AH2" si="0">$B2</f>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="E2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="T2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="U2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="V2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="W2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="X2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="Y2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="Z2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="AA2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="AB2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="AC2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="AD2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="AE2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="AF2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="AG2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
       <c r="AH2">
         <f t="shared" si="0"/>
-        <v>0.6232789702925996</v>
+        <v>0.55552581700052772</v>
       </c>
     </row>
   </sheetData>
@@ -1396,6 +1507,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -1539,15 +1659,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -1555,13 +1666,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{875FC4B3-9A2A-4712-AC67-992B5C967584}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709BD77E-23C7-49DD-BAC3-542011F7EA26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709BD77E-23C7-49DD-BAC3-542011F7EA26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{875FC4B3-9A2A-4712-AC67-992B5C967584}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C631C80F-86CB-44E5-A3E5-95908B2A278D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C631C80F-86CB-44E5-A3E5-95908B2A278D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>